--- a/artfynd/A 1375-2024 artfynd.xlsx
+++ b/artfynd/A 1375-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 1375-2024 artfynd.xlsx
+++ b/artfynd/A 1375-2024 artfynd.xlsx
@@ -9905,7 +9905,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>117668567</v>
+        <v>117668722</v>
       </c>
       <c r="B84" t="n">
         <v>90519</v>
@@ -9956,10 +9956,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>569878</v>
+        <v>570007</v>
       </c>
       <c r="R84" t="n">
-        <v>6426159</v>
+        <v>6426188</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10019,10 +10019,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>117668813</v>
+        <v>117668873</v>
       </c>
       <c r="B85" t="n">
-        <v>57534</v>
+        <v>97836</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10031,39 +10031,35 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>103012</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K85" t="inlineStr"/>
       <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
@@ -10071,13 +10067,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>570073</v>
+        <v>569996</v>
       </c>
       <c r="R85" t="n">
-        <v>6426155</v>
+        <v>6426247</v>
       </c>
       <c r="S85" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10109,17 +10105,13 @@
           <t>2024-06-09</t>
         </is>
       </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Även mkt sång</t>
-        </is>
-      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
       <c r="AE85" t="b">
         <v>0</v>
       </c>
+      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
@@ -10252,7 +10244,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>117668537</v>
+        <v>117668463</v>
       </c>
       <c r="B87" t="n">
         <v>90519</v>
@@ -10287,7 +10279,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -10303,10 +10295,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>569854</v>
+        <v>569868</v>
       </c>
       <c r="R87" t="n">
-        <v>6426197</v>
+        <v>6426200</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10366,10 +10358,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>117668873</v>
+        <v>117668537</v>
       </c>
       <c r="B88" t="n">
-        <v>97836</v>
+        <v>90519</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10378,35 +10370,38 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
       <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
@@ -10414,10 +10409,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>569996</v>
+        <v>569854</v>
       </c>
       <c r="R88" t="n">
-        <v>6426247</v>
+        <v>6426197</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10477,10 +10472,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>117668435</v>
+        <v>117668774</v>
       </c>
       <c r="B89" t="n">
-        <v>97836</v>
+        <v>104929</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10489,25 +10484,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10525,10 +10520,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>569895</v>
+        <v>570099</v>
       </c>
       <c r="R89" t="n">
-        <v>6426272</v>
+        <v>6426168</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10588,10 +10583,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>117668722</v>
+        <v>117668749</v>
       </c>
       <c r="B90" t="n">
-        <v>90519</v>
+        <v>97836</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10600,38 +10595,35 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="J90" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
       <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
@@ -10639,10 +10631,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>570007</v>
+        <v>570052</v>
       </c>
       <c r="R90" t="n">
-        <v>6426188</v>
+        <v>6426176</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10702,10 +10694,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>117668689</v>
+        <v>117668598</v>
       </c>
       <c r="B91" t="n">
-        <v>90902</v>
+        <v>90519</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10714,30 +10706,30 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>5420</v>
+        <v>5442</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -10753,10 +10745,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>569994</v>
+        <v>569892</v>
       </c>
       <c r="R91" t="n">
-        <v>6426204</v>
+        <v>6426161</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10816,10 +10808,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>117668598</v>
+        <v>117668435</v>
       </c>
       <c r="B92" t="n">
-        <v>90519</v>
+        <v>97836</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10828,38 +10820,35 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
       <c r="J92" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
       <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
@@ -10867,10 +10856,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>569892</v>
+        <v>569895</v>
       </c>
       <c r="R92" t="n">
-        <v>6426161</v>
+        <v>6426272</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10930,10 +10919,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>117668513</v>
+        <v>117668567</v>
       </c>
       <c r="B93" t="n">
-        <v>90902</v>
+        <v>90519</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10942,25 +10931,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>5420</v>
+        <v>5442</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -10981,10 +10970,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>569870</v>
+        <v>569878</v>
       </c>
       <c r="R93" t="n">
-        <v>6426197</v>
+        <v>6426159</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11044,10 +11033,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>117668749</v>
+        <v>117668513</v>
       </c>
       <c r="B94" t="n">
-        <v>97836</v>
+        <v>90902</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11056,35 +11045,38 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
       <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
@@ -11092,10 +11084,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>570052</v>
+        <v>569870</v>
       </c>
       <c r="R94" t="n">
-        <v>6426176</v>
+        <v>6426197</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11155,10 +11147,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>117668774</v>
+        <v>117668689</v>
       </c>
       <c r="B95" t="n">
-        <v>104929</v>
+        <v>90902</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11171,31 +11163,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>221144</v>
+        <v>5420</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
       <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
@@ -11203,10 +11198,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>570099</v>
+        <v>569994</v>
       </c>
       <c r="R95" t="n">
-        <v>6426168</v>
+        <v>6426204</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11266,10 +11261,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>117668463</v>
+        <v>117668813</v>
       </c>
       <c r="B96" t="n">
-        <v>90519</v>
+        <v>57534</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11282,21 +11277,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>5442</v>
+        <v>103012</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -11304,12 +11299,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
@@ -11317,13 +11313,13 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>569868</v>
+        <v>570073</v>
       </c>
       <c r="R96" t="n">
-        <v>6426200</v>
+        <v>6426155</v>
       </c>
       <c r="S96" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11355,13 +11351,17 @@
           <t>2024-06-09</t>
         </is>
       </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Även mkt sång</t>
+        </is>
+      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
       <c r="AE96" t="b">
         <v>0</v>
       </c>
-      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 1375-2024 artfynd.xlsx
+++ b/artfynd/A 1375-2024 artfynd.xlsx
@@ -9905,10 +9905,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>117668722</v>
+        <v>117668598</v>
       </c>
       <c r="B84" t="n">
-        <v>90519</v>
+        <v>90521</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9956,10 +9956,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>570007</v>
+        <v>569892</v>
       </c>
       <c r="R84" t="n">
-        <v>6426188</v>
+        <v>6426161</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10019,10 +10019,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>117668873</v>
+        <v>117668435</v>
       </c>
       <c r="B85" t="n">
-        <v>97836</v>
+        <v>97838</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10067,10 +10067,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>569996</v>
+        <v>569895</v>
       </c>
       <c r="R85" t="n">
-        <v>6426247</v>
+        <v>6426272</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10130,10 +10130,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>117668652</v>
+        <v>117668722</v>
       </c>
       <c r="B86" t="n">
-        <v>90499</v>
+        <v>90521</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10146,21 +10146,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1202</v>
+        <v>5442</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -10170,7 +10170,7 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K86" t="inlineStr"/>
@@ -10181,10 +10181,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>570014</v>
+        <v>570007</v>
       </c>
       <c r="R86" t="n">
-        <v>6426199</v>
+        <v>6426188</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10244,10 +10244,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>117668463</v>
+        <v>117668873</v>
       </c>
       <c r="B87" t="n">
-        <v>90519</v>
+        <v>97838</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10256,38 +10256,35 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
       <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
@@ -10295,10 +10292,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>569868</v>
+        <v>569996</v>
       </c>
       <c r="R87" t="n">
-        <v>6426200</v>
+        <v>6426247</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10358,10 +10355,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>117668537</v>
+        <v>117668689</v>
       </c>
       <c r="B88" t="n">
-        <v>90519</v>
+        <v>90904</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10370,25 +10367,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>5442</v>
+        <v>5420</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -10409,10 +10406,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>569854</v>
+        <v>569994</v>
       </c>
       <c r="R88" t="n">
-        <v>6426197</v>
+        <v>6426204</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10472,10 +10469,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>117668774</v>
+        <v>117668567</v>
       </c>
       <c r="B89" t="n">
-        <v>104929</v>
+        <v>90521</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10484,35 +10481,38 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>221144</v>
+        <v>5442</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
       <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
@@ -10520,10 +10520,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>570099</v>
+        <v>569878</v>
       </c>
       <c r="R89" t="n">
-        <v>6426168</v>
+        <v>6426159</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10583,10 +10583,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>117668749</v>
+        <v>117668463</v>
       </c>
       <c r="B90" t="n">
-        <v>97836</v>
+        <v>90521</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10595,35 +10595,38 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
       <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
@@ -10631,10 +10634,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>570052</v>
+        <v>569868</v>
       </c>
       <c r="R90" t="n">
-        <v>6426176</v>
+        <v>6426200</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10694,10 +10697,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>117668598</v>
+        <v>117668749</v>
       </c>
       <c r="B91" t="n">
-        <v>90519</v>
+        <v>97838</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10706,38 +10709,35 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
       <c r="J91" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
       <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
@@ -10745,10 +10745,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>569892</v>
+        <v>570052</v>
       </c>
       <c r="R91" t="n">
-        <v>6426161</v>
+        <v>6426176</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10808,10 +10808,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>117668435</v>
+        <v>117668774</v>
       </c>
       <c r="B92" t="n">
-        <v>97836</v>
+        <v>104931</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10820,25 +10820,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10856,10 +10856,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>569895</v>
+        <v>570099</v>
       </c>
       <c r="R92" t="n">
-        <v>6426272</v>
+        <v>6426168</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10919,10 +10919,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>117668567</v>
+        <v>117668813</v>
       </c>
       <c r="B93" t="n">
-        <v>90519</v>
+        <v>57535</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10935,21 +10935,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>5442</v>
+        <v>103012</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -10957,12 +10957,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
@@ -10970,13 +10971,13 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>569878</v>
+        <v>570073</v>
       </c>
       <c r="R93" t="n">
-        <v>6426159</v>
+        <v>6426155</v>
       </c>
       <c r="S93" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -11008,13 +11009,17 @@
           <t>2024-06-09</t>
         </is>
       </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>Även mkt sång</t>
+        </is>
+      </c>
       <c r="AD93" t="b">
         <v>0</v>
       </c>
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -11036,7 +11041,7 @@
         <v>117668513</v>
       </c>
       <c r="B94" t="n">
-        <v>90902</v>
+        <v>90904</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11147,10 +11152,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>117668689</v>
+        <v>117668537</v>
       </c>
       <c r="B95" t="n">
-        <v>90902</v>
+        <v>90521</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11159,25 +11164,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>5420</v>
+        <v>5442</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -11198,10 +11203,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>569994</v>
+        <v>569854</v>
       </c>
       <c r="R95" t="n">
-        <v>6426204</v>
+        <v>6426197</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11261,10 +11266,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>117668813</v>
+        <v>117668652</v>
       </c>
       <c r="B96" t="n">
-        <v>57534</v>
+        <v>90501</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11277,21 +11282,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>103012</v>
+        <v>1202</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -11299,13 +11304,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
@@ -11313,13 +11317,13 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>570073</v>
+        <v>570014</v>
       </c>
       <c r="R96" t="n">
-        <v>6426155</v>
+        <v>6426199</v>
       </c>
       <c r="S96" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11351,17 +11355,13 @@
           <t>2024-06-09</t>
         </is>
       </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Även mkt sång</t>
-        </is>
-      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 1375-2024 artfynd.xlsx
+++ b/artfynd/A 1375-2024 artfynd.xlsx
@@ -9905,10 +9905,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>117668598</v>
+        <v>117668435</v>
       </c>
       <c r="B84" t="n">
-        <v>90521</v>
+        <v>97838</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9917,38 +9917,35 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
@@ -9956,10 +9953,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>569892</v>
+        <v>569895</v>
       </c>
       <c r="R84" t="n">
-        <v>6426161</v>
+        <v>6426272</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10019,10 +10016,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>117668435</v>
+        <v>117668598</v>
       </c>
       <c r="B85" t="n">
-        <v>97838</v>
+        <v>90521</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10031,35 +10028,38 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
       <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
@@ -10067,10 +10067,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>569895</v>
+        <v>569892</v>
       </c>
       <c r="R85" t="n">
-        <v>6426272</v>
+        <v>6426161</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>

--- a/artfynd/A 1375-2024 artfynd.xlsx
+++ b/artfynd/A 1375-2024 artfynd.xlsx
@@ -11844,10 +11844,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>118485497</v>
+        <v>118485755</v>
       </c>
       <c r="B101" t="n">
-        <v>57306</v>
+        <v>97846</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11856,39 +11856,35 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K101" t="inlineStr"/>
       <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
@@ -11896,13 +11892,13 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>569919</v>
+        <v>570089</v>
       </c>
       <c r="R101" t="n">
-        <v>6426271</v>
+        <v>6426126</v>
       </c>
       <c r="S101" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11940,6 +11936,7 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
+      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
@@ -11958,10 +11955,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>118485755</v>
+        <v>118485497</v>
       </c>
       <c r="B102" t="n">
-        <v>97846</v>
+        <v>57306</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11970,35 +11967,39 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K102" t="inlineStr"/>
       <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
@@ -12006,13 +12007,13 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>570089</v>
+        <v>569919</v>
       </c>
       <c r="R102" t="n">
-        <v>6426126</v>
+        <v>6426271</v>
       </c>
       <c r="S102" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -12050,7 +12051,6 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
-      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 1375-2024 artfynd.xlsx
+++ b/artfynd/A 1375-2024 artfynd.xlsx
@@ -11844,10 +11844,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>118485755</v>
+        <v>118485497</v>
       </c>
       <c r="B101" t="n">
-        <v>97846</v>
+        <v>57306</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11856,35 +11856,39 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K101" t="inlineStr"/>
       <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
@@ -11892,13 +11896,13 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>570089</v>
+        <v>569919</v>
       </c>
       <c r="R101" t="n">
-        <v>6426126</v>
+        <v>6426271</v>
       </c>
       <c r="S101" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11936,7 +11940,6 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
-      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
@@ -11955,10 +11958,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>118485497</v>
+        <v>118485755</v>
       </c>
       <c r="B102" t="n">
-        <v>57306</v>
+        <v>97846</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11967,39 +11970,35 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K102" t="inlineStr"/>
       <c r="L102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
@@ -12007,13 +12006,13 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>569919</v>
+        <v>570089</v>
       </c>
       <c r="R102" t="n">
-        <v>6426271</v>
+        <v>6426126</v>
       </c>
       <c r="S102" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -12051,6 +12050,7 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
+      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 1375-2024 artfynd.xlsx
+++ b/artfynd/A 1375-2024 artfynd.xlsx
@@ -11380,10 +11380,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>118485733</v>
+        <v>118486070</v>
       </c>
       <c r="B97" t="n">
-        <v>97846</v>
+        <v>91127</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11392,39 +11392,38 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>220787</v>
+        <v>6031</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr"/>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L97" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr"/>
       <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
@@ -11432,10 +11431,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>570045</v>
+        <v>569832</v>
       </c>
       <c r="R97" t="n">
-        <v>6426142</v>
+        <v>6426225</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11495,10 +11494,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>118485535</v>
+        <v>118485781</v>
       </c>
       <c r="B98" t="n">
-        <v>56502</v>
+        <v>97846</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11507,35 +11506,39 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="K98" t="inlineStr"/>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
@@ -11543,10 +11546,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>569919</v>
+        <v>570094</v>
       </c>
       <c r="R98" t="n">
-        <v>6426271</v>
+        <v>6426142</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11581,17 +11584,13 @@
           <t>2024-07-16</t>
         </is>
       </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>Tjädertall, mkt äldre spillning</t>
-        </is>
-      </c>
       <c r="AD98" t="b">
         <v>0</v>
       </c>
       <c r="AE98" t="b">
         <v>0</v>
       </c>
+      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -11610,10 +11609,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>118486279</v>
+        <v>118485535</v>
       </c>
       <c r="B99" t="n">
-        <v>97846</v>
+        <v>56502</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11622,54 +11621,46 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
       <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>A 1370, Hackenäs, Sm</t>
+          <t>A 1375, Hackenäs, Sm</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>569898</v>
+        <v>569919</v>
       </c>
       <c r="R99" t="n">
-        <v>6426040</v>
+        <v>6426271</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11704,13 +11695,17 @@
           <t>2024-07-16</t>
         </is>
       </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Tjädertall, mkt äldre spillning</t>
+        </is>
+      </c>
       <c r="AD99" t="b">
         <v>0</v>
       </c>
       <c r="AE99" t="b">
         <v>0</v>
       </c>
-      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
@@ -11729,7 +11724,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>118485781</v>
+        <v>118485733</v>
       </c>
       <c r="B100" t="n">
         <v>97846</v>
@@ -11781,7 +11776,7 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>570094</v>
+        <v>570045</v>
       </c>
       <c r="R100" t="n">
         <v>6426142</v>
@@ -12188,10 +12183,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>118486070</v>
+        <v>118485418</v>
       </c>
       <c r="B104" t="n">
-        <v>91127</v>
+        <v>90524</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -12200,30 +12195,30 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6031</v>
+        <v>5442</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -12239,10 +12234,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>569832</v>
+        <v>570059</v>
       </c>
       <c r="R104" t="n">
-        <v>6426225</v>
+        <v>6426256</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12417,10 +12412,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>118485418</v>
+        <v>118486279</v>
       </c>
       <c r="B106" t="n">
-        <v>90524</v>
+        <v>97846</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12429,49 +12424,54 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K106" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr"/>
       <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>A 1375, Hackenäs, Sm</t>
+          <t>A 1370, Hackenäs, Sm</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>570059</v>
+        <v>569898</v>
       </c>
       <c r="R106" t="n">
-        <v>6426256</v>
+        <v>6426040</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12638,7 +12638,7 @@
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Ann Newsome, Sven Halling, Eddy Kasselstrand, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Eddy Kasselstrand, Sven Halling, Ann Newsome</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>

--- a/artfynd/A 1375-2024 artfynd.xlsx
+++ b/artfynd/A 1375-2024 artfynd.xlsx
@@ -11380,10 +11380,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>118486070</v>
+        <v>118485781</v>
       </c>
       <c r="B97" t="n">
-        <v>91127</v>
+        <v>97846</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11392,38 +11392,39 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6031</v>
+        <v>220787</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr"/>
       <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
@@ -11431,10 +11432,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>569832</v>
+        <v>570094</v>
       </c>
       <c r="R97" t="n">
-        <v>6426225</v>
+        <v>6426142</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11494,10 +11495,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>118485781</v>
+        <v>118486070</v>
       </c>
       <c r="B98" t="n">
-        <v>97846</v>
+        <v>91127</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11506,39 +11507,38 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>220787</v>
+        <v>6031</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr"/>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L98" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr"/>
       <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
@@ -11546,10 +11546,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>570094</v>
+        <v>569832</v>
       </c>
       <c r="R98" t="n">
-        <v>6426142</v>
+        <v>6426225</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11609,10 +11609,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>118485535</v>
+        <v>118485497</v>
       </c>
       <c r="B99" t="n">
-        <v>56502</v>
+        <v>57306</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11621,33 +11621,37 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K99" t="inlineStr"/>
       <c r="L99" t="inlineStr"/>
       <c r="M99" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N99" t="inlineStr"/>
@@ -11663,7 +11667,7 @@
         <v>6426271</v>
       </c>
       <c r="S99" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11693,11 +11697,6 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2024-07-16</t>
-        </is>
-      </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>Tjädertall, mkt äldre spillning</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11724,10 +11723,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>118485733</v>
+        <v>118485535</v>
       </c>
       <c r="B100" t="n">
-        <v>97846</v>
+        <v>56502</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11736,39 +11735,35 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K100" t="inlineStr"/>
       <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
@@ -11776,10 +11771,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>570045</v>
+        <v>569919</v>
       </c>
       <c r="R100" t="n">
-        <v>6426142</v>
+        <v>6426271</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11814,13 +11809,17 @@
           <t>2024-07-16</t>
         </is>
       </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Tjädertall, mkt äldre spillning</t>
+        </is>
+      </c>
       <c r="AD100" t="b">
         <v>0</v>
       </c>
       <c r="AE100" t="b">
         <v>0</v>
       </c>
-      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
@@ -11839,10 +11838,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>118485497</v>
+        <v>118485733</v>
       </c>
       <c r="B101" t="n">
-        <v>57306</v>
+        <v>97846</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11851,39 +11850,39 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K101" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
@@ -11891,13 +11890,13 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>569919</v>
+        <v>570045</v>
       </c>
       <c r="R101" t="n">
-        <v>6426271</v>
+        <v>6426142</v>
       </c>
       <c r="S101" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11935,6 +11934,7 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
+      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 1375-2024 artfynd.xlsx
+++ b/artfynd/A 1375-2024 artfynd.xlsx
@@ -11380,10 +11380,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>118485781</v>
+        <v>118485535</v>
       </c>
       <c r="B97" t="n">
-        <v>97846</v>
+        <v>56502</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11392,39 +11392,35 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K97" t="inlineStr"/>
       <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
@@ -11432,10 +11428,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>570094</v>
+        <v>569919</v>
       </c>
       <c r="R97" t="n">
-        <v>6426142</v>
+        <v>6426271</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11470,13 +11466,17 @@
           <t>2024-07-16</t>
         </is>
       </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Tjädertall, mkt äldre spillning</t>
+        </is>
+      </c>
       <c r="AD97" t="b">
         <v>0</v>
       </c>
       <c r="AE97" t="b">
         <v>0</v>
       </c>
-      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -11495,10 +11495,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>118486070</v>
+        <v>118486193</v>
       </c>
       <c r="B98" t="n">
-        <v>91127</v>
+        <v>97846</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11507,38 +11507,43 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6031</v>
+        <v>220787</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr"/>
       <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
@@ -11546,10 +11551,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>569832</v>
+        <v>570096</v>
       </c>
       <c r="R98" t="n">
-        <v>6426225</v>
+        <v>6426155</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11609,10 +11614,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>118485497</v>
+        <v>118486070</v>
       </c>
       <c r="B99" t="n">
-        <v>57306</v>
+        <v>91127</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11621,25 +11626,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100049</v>
+        <v>6031</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -11647,13 +11652,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
@@ -11661,13 +11665,13 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>569919</v>
+        <v>569832</v>
       </c>
       <c r="R99" t="n">
-        <v>6426271</v>
+        <v>6426225</v>
       </c>
       <c r="S99" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11705,6 +11709,7 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
+      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
@@ -11723,10 +11728,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>118485535</v>
+        <v>118485781</v>
       </c>
       <c r="B100" t="n">
-        <v>56502</v>
+        <v>97846</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11735,35 +11740,39 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
@@ -11771,10 +11780,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>569919</v>
+        <v>570094</v>
       </c>
       <c r="R100" t="n">
-        <v>6426271</v>
+        <v>6426142</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11809,17 +11818,13 @@
           <t>2024-07-16</t>
         </is>
       </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>Tjädertall, mkt äldre spillning</t>
-        </is>
-      </c>
       <c r="AD100" t="b">
         <v>0</v>
       </c>
       <c r="AE100" t="b">
         <v>0</v>
       </c>
+      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
@@ -11838,7 +11843,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>118485733</v>
+        <v>118486036</v>
       </c>
       <c r="B101" t="n">
         <v>97846</v>
@@ -11890,10 +11895,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>570045</v>
+        <v>569845</v>
       </c>
       <c r="R101" t="n">
-        <v>6426142</v>
+        <v>6426218</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12064,7 +12069,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>118486193</v>
+        <v>118486279</v>
       </c>
       <c r="B103" t="n">
         <v>97846</v>
@@ -12099,7 +12104,7 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -12116,14 +12121,14 @@
       <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>A 1375, Hackenäs, Sm</t>
+          <t>A 1370, Hackenäs, Sm</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>570096</v>
+        <v>569898</v>
       </c>
       <c r="R103" t="n">
-        <v>6426155</v>
+        <v>6426040</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12183,10 +12188,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>118485418</v>
+        <v>118485497</v>
       </c>
       <c r="B104" t="n">
-        <v>90524</v>
+        <v>57306</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -12199,34 +12204,35 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
@@ -12234,13 +12240,13 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>570059</v>
+        <v>569919</v>
       </c>
       <c r="R104" t="n">
-        <v>6426256</v>
+        <v>6426271</v>
       </c>
       <c r="S104" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -12278,7 +12284,6 @@
       <c r="AE104" t="b">
         <v>0</v>
       </c>
-      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
@@ -12297,7 +12302,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>118486036</v>
+        <v>118485733</v>
       </c>
       <c r="B105" t="n">
         <v>97846</v>
@@ -12349,10 +12354,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>569845</v>
+        <v>570045</v>
       </c>
       <c r="R105" t="n">
-        <v>6426218</v>
+        <v>6426142</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12412,10 +12417,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>118486279</v>
+        <v>118485418</v>
       </c>
       <c r="B106" t="n">
-        <v>97846</v>
+        <v>90524</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12424,54 +12429,49 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K106" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L106" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr"/>
       <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>A 1370, Hackenäs, Sm</t>
+          <t>A 1375, Hackenäs, Sm</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>569898</v>
+        <v>570059</v>
       </c>
       <c r="R106" t="n">
-        <v>6426040</v>
+        <v>6426256</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>

--- a/artfynd/A 1375-2024 artfynd.xlsx
+++ b/artfynd/A 1375-2024 artfynd.xlsx
@@ -11380,10 +11380,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>118485535</v>
+        <v>118485418</v>
       </c>
       <c r="B97" t="n">
-        <v>56502</v>
+        <v>90531</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11392,35 +11392,38 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100138</v>
+        <v>5442</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
@@ -11428,10 +11431,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>569919</v>
+        <v>570059</v>
       </c>
       <c r="R97" t="n">
-        <v>6426271</v>
+        <v>6426256</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11466,17 +11469,13 @@
           <t>2024-07-16</t>
         </is>
       </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>Tjädertall, mkt äldre spillning</t>
-        </is>
-      </c>
       <c r="AD97" t="b">
         <v>0</v>
       </c>
       <c r="AE97" t="b">
         <v>0</v>
       </c>
+      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -11495,10 +11494,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>118486193</v>
+        <v>118485535</v>
       </c>
       <c r="B98" t="n">
-        <v>97846</v>
+        <v>56502</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11507,43 +11506,35 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
       <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
@@ -11551,10 +11542,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>570096</v>
+        <v>569919</v>
       </c>
       <c r="R98" t="n">
-        <v>6426155</v>
+        <v>6426271</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11589,13 +11580,17 @@
           <t>2024-07-16</t>
         </is>
       </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Tjädertall, mkt äldre spillning</t>
+        </is>
+      </c>
       <c r="AD98" t="b">
         <v>0</v>
       </c>
       <c r="AE98" t="b">
         <v>0</v>
       </c>
-      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -11614,10 +11609,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>118486070</v>
+        <v>118485781</v>
       </c>
       <c r="B99" t="n">
-        <v>91127</v>
+        <v>97853</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11626,38 +11621,39 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6031</v>
+        <v>220787</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
       <c r="J99" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr"/>
       <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
@@ -11665,10 +11661,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>569832</v>
+        <v>570094</v>
       </c>
       <c r="R99" t="n">
-        <v>6426225</v>
+        <v>6426142</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11728,10 +11724,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>118485781</v>
+        <v>118485755</v>
       </c>
       <c r="B100" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11767,11 +11763,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K100" t="inlineStr"/>
       <c r="L100" t="inlineStr"/>
       <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
@@ -11780,10 +11772,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>570094</v>
+        <v>570089</v>
       </c>
       <c r="R100" t="n">
-        <v>6426142</v>
+        <v>6426126</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11843,10 +11835,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>118486036</v>
+        <v>118486193</v>
       </c>
       <c r="B101" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11876,7 +11868,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I101" t="inlineStr"/>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="J101" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -11895,10 +11891,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>569845</v>
+        <v>570096</v>
       </c>
       <c r="R101" t="n">
-        <v>6426218</v>
+        <v>6426155</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11958,10 +11954,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>118485755</v>
+        <v>118486279</v>
       </c>
       <c r="B102" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11991,25 +11987,33 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I102" t="inlineStr"/>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="J102" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr"/>
       <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>A 1375, Hackenäs, Sm</t>
+          <t>A 1370, Hackenäs, Sm</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>570089</v>
+        <v>569898</v>
       </c>
       <c r="R102" t="n">
-        <v>6426126</v>
+        <v>6426040</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12069,10 +12073,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>118486279</v>
+        <v>118485733</v>
       </c>
       <c r="B103" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12102,11 +12106,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+      <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -12121,14 +12121,14 @@
       <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>A 1370, Hackenäs, Sm</t>
+          <t>A 1375, Hackenäs, Sm</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>569898</v>
+        <v>570045</v>
       </c>
       <c r="R103" t="n">
-        <v>6426040</v>
+        <v>6426142</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12188,10 +12188,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>118485497</v>
+        <v>118486070</v>
       </c>
       <c r="B104" t="n">
-        <v>57306</v>
+        <v>91134</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -12200,25 +12200,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100049</v>
+        <v>6031</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -12226,13 +12226,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K104" t="inlineStr"/>
-      <c r="L104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
@@ -12240,13 +12239,13 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>569919</v>
+        <v>569832</v>
       </c>
       <c r="R104" t="n">
-        <v>6426271</v>
+        <v>6426225</v>
       </c>
       <c r="S104" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -12284,6 +12283,7 @@
       <c r="AE104" t="b">
         <v>0</v>
       </c>
+      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
@@ -12302,10 +12302,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>118485733</v>
+        <v>118486036</v>
       </c>
       <c r="B105" t="n">
-        <v>97846</v>
+        <v>97853</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -12354,10 +12354,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>570045</v>
+        <v>569845</v>
       </c>
       <c r="R105" t="n">
-        <v>6426142</v>
+        <v>6426218</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12417,10 +12417,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>118485418</v>
+        <v>118485497</v>
       </c>
       <c r="B106" t="n">
-        <v>90524</v>
+        <v>57306</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12433,34 +12433,35 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J106" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
@@ -12468,13 +12469,13 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>570059</v>
+        <v>569919</v>
       </c>
       <c r="R106" t="n">
-        <v>6426256</v>
+        <v>6426271</v>
       </c>
       <c r="S106" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -12512,7 +12513,6 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
-      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>
@@ -12534,7 +12534,7 @@
         <v>118485708</v>
       </c>
       <c r="B107" t="n">
-        <v>89999</v>
+        <v>90006</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>

--- a/artfynd/A 1375-2024 artfynd.xlsx
+++ b/artfynd/A 1375-2024 artfynd.xlsx
@@ -11380,10 +11380,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>118485418</v>
+        <v>118485733</v>
       </c>
       <c r="B97" t="n">
-        <v>90531</v>
+        <v>97853</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11392,38 +11392,39 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
       <c r="J97" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr"/>
       <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
@@ -11431,10 +11432,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>570059</v>
+        <v>570045</v>
       </c>
       <c r="R97" t="n">
-        <v>6426256</v>
+        <v>6426142</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11494,10 +11495,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>118485535</v>
+        <v>118485497</v>
       </c>
       <c r="B98" t="n">
-        <v>56502</v>
+        <v>57306</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11506,33 +11507,37 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K98" t="inlineStr"/>
       <c r="L98" t="inlineStr"/>
       <c r="M98" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N98" t="inlineStr"/>
@@ -11548,7 +11553,7 @@
         <v>6426271</v>
       </c>
       <c r="S98" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11578,11 +11583,6 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2024-07-16</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>Tjädertall, mkt äldre spillning</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11609,10 +11609,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>118485781</v>
+        <v>118486070</v>
       </c>
       <c r="B99" t="n">
-        <v>97853</v>
+        <v>91134</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11621,39 +11621,38 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>220787</v>
+        <v>6031</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr"/>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L99" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr"/>
       <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
@@ -11661,10 +11660,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>570094</v>
+        <v>569832</v>
       </c>
       <c r="R99" t="n">
-        <v>6426142</v>
+        <v>6426225</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11717,14 +11716,14 @@
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Eddy Kasselstrand, Sven Halling, Ann Newsome</t>
+          <t>Eddy Kasselstrand, Sven Halling, Ann Newsome, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>118485755</v>
+        <v>118486036</v>
       </c>
       <c r="B100" t="n">
         <v>97853</v>
@@ -11763,7 +11762,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr"/>
       <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
@@ -11772,10 +11775,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>570089</v>
+        <v>569845</v>
       </c>
       <c r="R100" t="n">
-        <v>6426126</v>
+        <v>6426218</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11835,10 +11838,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>118486193</v>
+        <v>118485535</v>
       </c>
       <c r="B101" t="n">
-        <v>97853</v>
+        <v>56502</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11847,43 +11850,35 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
       <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
@@ -11891,10 +11886,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>570096</v>
+        <v>569919</v>
       </c>
       <c r="R101" t="n">
-        <v>6426155</v>
+        <v>6426271</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11929,13 +11924,17 @@
           <t>2024-07-16</t>
         </is>
       </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>Tjädertall, mkt äldre spillning</t>
+        </is>
+      </c>
       <c r="AD101" t="b">
         <v>0</v>
       </c>
       <c r="AE101" t="b">
         <v>0</v>
       </c>
-      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
@@ -11954,7 +11953,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>118486279</v>
+        <v>118485781</v>
       </c>
       <c r="B102" t="n">
         <v>97853</v>
@@ -11987,11 +11986,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+      <c r="I102" t="inlineStr"/>
       <c r="J102" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -12006,14 +12001,14 @@
       <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>A 1370, Hackenäs, Sm</t>
+          <t>A 1375, Hackenäs, Sm</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>569898</v>
+        <v>570094</v>
       </c>
       <c r="R102" t="n">
-        <v>6426040</v>
+        <v>6426142</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12073,7 +12068,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>118485733</v>
+        <v>118485755</v>
       </c>
       <c r="B103" t="n">
         <v>97853</v>
@@ -12112,11 +12107,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K103" t="inlineStr"/>
       <c r="L103" t="inlineStr"/>
       <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
@@ -12125,10 +12116,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>570045</v>
+        <v>570089</v>
       </c>
       <c r="R103" t="n">
-        <v>6426142</v>
+        <v>6426126</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12188,10 +12179,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>118486070</v>
+        <v>118485418</v>
       </c>
       <c r="B104" t="n">
-        <v>91134</v>
+        <v>90531</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -12200,30 +12191,30 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6031</v>
+        <v>5442</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
@@ -12239,10 +12230,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>569832</v>
+        <v>570059</v>
       </c>
       <c r="R104" t="n">
-        <v>6426225</v>
+        <v>6426256</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12302,7 +12293,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>118486036</v>
+        <v>118486193</v>
       </c>
       <c r="B105" t="n">
         <v>97853</v>
@@ -12335,7 +12326,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I105" t="inlineStr"/>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="J105" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -12354,10 +12349,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>569845</v>
+        <v>570096</v>
       </c>
       <c r="R105" t="n">
-        <v>6426218</v>
+        <v>6426155</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12417,10 +12412,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>118485497</v>
+        <v>118486279</v>
       </c>
       <c r="B106" t="n">
-        <v>57306</v>
+        <v>97853</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12429,53 +12424,57 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K106" t="inlineStr"/>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr"/>
-      <c r="M106" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>A 1375, Hackenäs, Sm</t>
+          <t>A 1370, Hackenäs, Sm</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>569919</v>
+        <v>569898</v>
       </c>
       <c r="R106" t="n">
-        <v>6426271</v>
+        <v>6426040</v>
       </c>
       <c r="S106" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -12513,6 +12512,7 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
+      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 1375-2024 artfynd.xlsx
+++ b/artfynd/A 1375-2024 artfynd.xlsx
@@ -12648,7 +12648,7 @@
         <v>120861172</v>
       </c>
       <c r="B108" t="n">
-        <v>91305</v>
+        <v>91315</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
